--- a/data/trans_bre/P16A06-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Edad-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,42; 2,37</t>
+          <t>0,23; 2,25</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,75</t>
+          <t>0,27; 2,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,89</t>
+          <t>0,25; 2,82</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 7,09</t>
+          <t>-0,36; 6,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,69</t>
+          <t>-0,5; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 1,25</t>
+          <t>-1,26; 1,36</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,82</t>
+          <t>0,0; 2,08</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,39</t>
+          <t>-0,57; 2,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,88; 509,7</t>
+          <t>-60,2; 607,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 339,41</t>
+          <t>-85,18; 517,32</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-55,18; —</t>
+          <t>-52,55; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-69,33; 1801,66</t>
+          <t>-80,85; 1511,72</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,52; 2,46</t>
+          <t>-0,48; 2,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,12</t>
+          <t>0,25; 4,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,71</t>
+          <t>0,18; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,87; 3,32</t>
+          <t>-0,95; 3,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-29,47; 332,42</t>
+          <t>-33,38; 290,14</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-5,83; 302,2</t>
+          <t>1,01; 291,15</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-17,83; 772,63</t>
+          <t>-6,91; 787,73</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-23,26; 214,04</t>
+          <t>-26,7; 215,85</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,08; 4,2</t>
+          <t>0,07; 4,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,61</t>
+          <t>0,78; 5,79</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,55; 6,53</t>
+          <t>1,65; 6,67</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1,97; 8,4</t>
+          <t>2,09; 8,33</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 365,49</t>
+          <t>-6,61; 529,63</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 376,05</t>
+          <t>17,06; 392,26</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>37,48; 330,03</t>
+          <t>39,77; 329,72</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>38,13; 485,13</t>
+          <t>39,67; 446,0</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 6,96</t>
+          <t>1,28; 7,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 8,18</t>
+          <t>2,6; 8,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,0; 13,73</t>
+          <t>6,04; 13,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,79; 10,6</t>
+          <t>4,46; 10,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 487,78</t>
+          <t>18,15; 496,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,62; 613,99</t>
+          <t>51,4; 660,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>112,84; 627,69</t>
+          <t>98,79; 540,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,02; 193,66</t>
+          <t>53,9; 197,0</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,37; 7,68</t>
+          <t>0,2; 7,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,69; 12,68</t>
+          <t>4,14; 12,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,81; 15,02</t>
+          <t>5,45; 15,12</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 8,44</t>
+          <t>-5,84; 8,41</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-3,95; 218,87</t>
+          <t>-1,7; 218,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>77,07; 733,44</t>
+          <t>73,52; 725,31</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>60,97; 291,61</t>
+          <t>56,59; 299,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-48,78; 102,36</t>
+          <t>-55,04; 104,18</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 6,96</t>
+          <t>-2,82; 7,48</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,66; 18,56</t>
+          <t>8,7; 18,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,07; 12,54</t>
+          <t>2,31; 12,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,56; 15,98</t>
+          <t>6,45; 15,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,8; 128,02</t>
+          <t>-29,51; 135,31</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>112,14; 617,83</t>
+          <t>103,67; 641,84</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,14; 211,45</t>
+          <t>19,9; 205,87</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>35,55; 120,9</t>
+          <t>33,48; 118,09</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,07</t>
+          <t>1,37; 3,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,19; 5,29</t>
+          <t>3,17; 5,18</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,81; 5,95</t>
+          <t>3,8; 6,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,35; 6,54</t>
+          <t>2,96; 6,42</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>58,98; 192,36</t>
+          <t>57,82; 186,96</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>124,9; 305,31</t>
+          <t>124,49; 312,54</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>123,51; 268,22</t>
+          <t>120,81; 265,86</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>62,99; 158,24</t>
+          <t>60,65; 167,14</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P16A06-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P16A06-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,25</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>275,97%</t>
+          <t>180,02%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,23; 2,25</t>
+          <t>0,38; 2,37</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,27; 2,6</t>
+          <t>0,26; 2,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,82</t>
+          <t>0,25; 3,11</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 6,7</t>
+          <t>-0,88; 6,32</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,74</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>112,18%</t>
+          <t>32,53%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 1,65</t>
+          <t>-0,51; 1,65</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 1,36</t>
+          <t>-1,34; 1,25</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,08</t>
+          <t>-0,01; 1,99</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-0,57; 2,3</t>
+          <t>-1,28; 1,99</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-60,2; 607,74</t>
+          <t>-64,43; 465,93</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-85,18; 517,32</t>
+          <t>-100,0; 336,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-52,55; —</t>
+          <t>-51,41; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,85; 1511,72</t>
+          <t>-78,48; 541,64</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1,34</t>
+          <t>1,5</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>59,59%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,39</t>
+          <t>-0,43; 2,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 4,2</t>
+          <t>0,17; 4,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 2,86</t>
+          <t>0,22; 2,86</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 3,56</t>
+          <t>-0,72; 3,32</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-33,38; 290,14</t>
+          <t>-29,38; 351,11</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,01; 291,15</t>
+          <t>-3,53; 339,7</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 787,73</t>
+          <t>-4,09; 852,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-26,7; 215,85</t>
+          <t>-22,02; 200,22</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,76</t>
+          <t>2,89</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>138,11%</t>
+          <t>60,92%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 4,68</t>
+          <t>-0,03; 4,46</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,78; 5,79</t>
+          <t>0,89; 5,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 6,67</t>
+          <t>1,64; 6,36</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,09; 8,33</t>
+          <t>0,62; 5,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-6,61; 529,63</t>
+          <t>-12,04; 505,52</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>17,06; 392,26</t>
+          <t>19,46; 393,14</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>39,77; 329,72</t>
+          <t>32,79; 317,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>39,67; 446,0</t>
+          <t>8,36; 144,92</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7,76</t>
+          <t>7,95</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>114,78%</t>
+          <t>123,8%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,28; 7,04</t>
+          <t>1,24; 6,91</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,6; 8,5</t>
+          <t>2,46; 8,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,04; 13,24</t>
+          <t>5,82; 13,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>4,46; 10,44</t>
+          <t>4,99; 11,11</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>18,15; 496,43</t>
+          <t>20,52; 487,21</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>51,4; 660,1</t>
+          <t>50,29; 661,4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>98,79; 540,87</t>
+          <t>99,41; 568,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>53,9; 197,0</t>
+          <t>60,98; 234,44</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1,93</t>
+          <t>8,24</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>98,27%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,2; 7,87</t>
+          <t>0,26; 7,58</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4,14; 12,03</t>
+          <t>4,32; 12,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5,45; 15,12</t>
+          <t>5,77; 15,22</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-5,84; 8,41</t>
+          <t>4,67; 11,38</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 218,8</t>
+          <t>-0,66; 212,97</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>73,52; 725,31</t>
+          <t>66,04; 690,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>56,59; 299,48</t>
+          <t>51,97; 279,71</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-55,04; 104,18</t>
+          <t>45,43; 167,97</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11,31</t>
+          <t>11,24</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>70,69%</t>
+          <t>70,61%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,82; 7,48</t>
+          <t>-2,79; 7,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,7; 18,92</t>
+          <t>8,75; 18,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 12,58</t>
+          <t>1,51; 12,67</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,45; 15,93</t>
+          <t>6,56; 15,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-29,51; 135,31</t>
+          <t>-26,2; 141,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>103,67; 641,84</t>
+          <t>111,14; 650,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,9; 205,87</t>
+          <t>11,86; 198,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,48; 118,09</t>
+          <t>34,74; 121,2</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4,99</t>
+          <t>5,23</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>102,84%</t>
+          <t>101,63%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,02</t>
+          <t>1,39; 3,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>3,17; 5,18</t>
+          <t>3,22; 5,19</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>3,8; 6,04</t>
+          <t>3,83; 5,94</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>2,96; 6,42</t>
+          <t>4,15; 6,38</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>57,82; 186,96</t>
+          <t>59,81; 182,67</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>124,49; 312,54</t>
+          <t>127,29; 316,8</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>120,81; 265,86</t>
+          <t>122,72; 266,97</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>60,65; 167,14</t>
+          <t>73,06; 139,2</t>
         </is>
       </c>
     </row>
